--- a/Lista_Nacala_Porto_Turmas.xlsx
+++ b/Lista_Nacala_Porto_Turmas.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{F0ECD2CA-1AFC-4D72-92BC-085899DFC072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{806549D5-C47C-415C-A3F4-07E5F9C9B417}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{F0ECD2CA-1AFC-4D72-92BC-085899DFC072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72CCFE79-889A-4ACC-8210-E6E1F573723B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{619861BA-25F5-43D2-A075-305249973C9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$250</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1469,16 +1472,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156349CF-6280-4CD0-803A-013CF8C0A2F2}">
   <dimension ref="A1:G250"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>42</v>
       </c>
@@ -1524,7 +1527,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>42</v>
       </c>
@@ -1547,7 +1550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>42</v>
       </c>
@@ -1570,7 +1573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>42</v>
       </c>
@@ -1593,7 +1596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>42</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>42</v>
       </c>
@@ -1639,7 +1642,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>42</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>42</v>
       </c>
@@ -1685,7 +1688,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>42</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>42</v>
       </c>
@@ -1731,7 +1734,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>42</v>
       </c>
@@ -1777,7 +1780,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>42</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
@@ -1823,7 +1826,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
@@ -1846,7 +1849,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>42</v>
       </c>
@@ -1869,7 +1872,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
@@ -1892,7 +1895,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>42</v>
       </c>
@@ -1915,7 +1918,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
@@ -1938,7 +1941,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
@@ -1961,7 +1964,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>42</v>
       </c>
@@ -1984,7 +1987,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>42</v>
       </c>
@@ -2007,7 +2010,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>42</v>
       </c>
@@ -2030,7 +2033,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -2053,7 +2056,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>42</v>
       </c>
@@ -2076,7 +2079,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>42</v>
       </c>
@@ -2099,7 +2102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>42</v>
       </c>
@@ -2122,7 +2125,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>42</v>
       </c>
@@ -2145,7 +2148,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
@@ -2168,7 +2171,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>42</v>
       </c>
@@ -2191,7 +2194,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>42</v>
       </c>
@@ -2214,7 +2217,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>42</v>
       </c>
@@ -2237,7 +2240,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>42</v>
       </c>
@@ -2260,7 +2263,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>42</v>
       </c>
@@ -2283,7 +2286,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>42</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>42</v>
       </c>
@@ -2329,7 +2332,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -2352,7 +2355,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>42</v>
       </c>
@@ -2375,7 +2378,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2398,7 +2401,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>42</v>
       </c>
@@ -2421,7 +2424,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -2444,7 +2447,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>42</v>
       </c>
@@ -2467,7 +2470,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>42</v>
       </c>
@@ -2490,7 +2493,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -2513,7 +2516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>42</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>42</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>42</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>42</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>42</v>
       </c>
@@ -2628,7 +2631,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>42</v>
       </c>
@@ -2651,7 +2654,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>42</v>
       </c>
@@ -2674,7 +2677,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>42</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>42</v>
       </c>
@@ -2720,7 +2723,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>42</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>42</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>42</v>
       </c>
@@ -2789,7 +2792,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>42</v>
       </c>
@@ -2812,7 +2815,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>42</v>
       </c>
@@ -2835,7 +2838,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>42</v>
       </c>
@@ -2858,7 +2861,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>42</v>
       </c>
@@ -2881,7 +2884,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>42</v>
       </c>
@@ -2904,7 +2907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>42</v>
       </c>
@@ -2927,7 +2930,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>42</v>
       </c>
@@ -2950,7 +2953,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>42</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>42</v>
       </c>
@@ -2996,7 +2999,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>42</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>42</v>
       </c>
@@ -3042,7 +3045,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>42</v>
       </c>
@@ -3065,7 +3068,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>42</v>
       </c>
@@ -3088,7 +3091,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>42</v>
       </c>
@@ -3111,7 +3114,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>42</v>
       </c>
@@ -3134,7 +3137,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>42</v>
       </c>
@@ -3157,7 +3160,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>42</v>
       </c>
@@ -3180,7 +3183,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>42</v>
       </c>
@@ -3203,7 +3206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>42</v>
       </c>
@@ -3226,7 +3229,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>42</v>
       </c>
@@ -3249,7 +3252,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>42</v>
       </c>
@@ -3272,7 +3275,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>42</v>
       </c>
@@ -3295,7 +3298,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>42</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>42</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
         <v>42</v>
       </c>
@@ -3364,7 +3367,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>42</v>
       </c>
@@ -3387,7 +3390,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>42</v>
       </c>
@@ -3410,7 +3413,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>42</v>
       </c>
@@ -3433,7 +3436,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>42</v>
       </c>
@@ -3456,7 +3459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>42</v>
       </c>
@@ -3479,7 +3482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>42</v>
       </c>
@@ -3502,7 +3505,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>42</v>
       </c>
@@ -3525,7 +3528,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>42</v>
       </c>
@@ -3548,7 +3551,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>42</v>
       </c>
@@ -3571,7 +3574,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>42</v>
       </c>
@@ -3594,7 +3597,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>42</v>
       </c>
@@ -3617,7 +3620,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>42</v>
       </c>
@@ -3640,7 +3643,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>42</v>
       </c>
@@ -3663,7 +3666,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>42</v>
       </c>
@@ -3686,7 +3689,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>42</v>
       </c>
@@ -3709,7 +3712,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>42</v>
       </c>
@@ -3732,7 +3735,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>42</v>
       </c>
@@ -3755,7 +3758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>42</v>
       </c>
@@ -3778,7 +3781,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>42</v>
       </c>
@@ -3801,7 +3804,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>42</v>
       </c>
@@ -3824,7 +3827,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>42</v>
       </c>
@@ -3847,7 +3850,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>42</v>
       </c>
@@ -3870,7 +3873,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>42</v>
       </c>
@@ -3893,7 +3896,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>42</v>
       </c>
@@ -3916,7 +3919,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>42</v>
       </c>
@@ -3939,7 +3942,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>42</v>
       </c>
@@ -3962,7 +3965,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>42</v>
       </c>
@@ -3985,7 +3988,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>42</v>
       </c>
@@ -4008,7 +4011,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>42</v>
       </c>
@@ -4031,7 +4034,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>42</v>
       </c>
@@ -4054,7 +4057,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>42</v>
       </c>
@@ -4077,7 +4080,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>42</v>
       </c>
@@ -4100,7 +4103,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>42</v>
       </c>
@@ -4123,7 +4126,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>42</v>
       </c>
@@ -4146,7 +4149,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>42</v>
       </c>
@@ -4169,7 +4172,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>42</v>
       </c>
@@ -4192,7 +4195,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>42</v>
       </c>
@@ -4215,7 +4218,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>42</v>
       </c>
@@ -4238,7 +4241,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>42</v>
       </c>
@@ -4261,7 +4264,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>42</v>
       </c>
@@ -4284,7 +4287,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>42</v>
       </c>
@@ -4307,7 +4310,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
         <v>42</v>
       </c>
@@ -4330,7 +4333,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>42</v>
       </c>
@@ -4353,7 +4356,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
         <v>42</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>42</v>
       </c>
@@ -4399,7 +4402,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
         <v>42</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>42</v>
       </c>
@@ -4445,7 +4448,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>42</v>
       </c>
@@ -4468,7 +4471,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>42</v>
       </c>
@@ -4491,7 +4494,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>42</v>
       </c>
@@ -4514,7 +4517,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>42</v>
       </c>
@@ -4537,7 +4540,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
         <v>42</v>
       </c>
@@ -4560,7 +4563,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>42</v>
       </c>
@@ -4583,7 +4586,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
         <v>42</v>
       </c>
@@ -4606,7 +4609,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>42</v>
       </c>
@@ -4629,7 +4632,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>42</v>
       </c>
@@ -4652,7 +4655,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>42</v>
       </c>
@@ -4675,7 +4678,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>42</v>
       </c>
@@ -4698,7 +4701,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
         <v>42</v>
       </c>
@@ -4721,7 +4724,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
         <v>42</v>
       </c>
@@ -4744,7 +4747,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>42</v>
       </c>
@@ -4767,7 +4770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
         <v>42</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>42</v>
       </c>
@@ -4813,7 +4816,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
         <v>42</v>
       </c>
@@ -4836,7 +4839,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>42</v>
       </c>
@@ -4859,7 +4862,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
         <v>42</v>
       </c>
@@ -4882,7 +4885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>42</v>
       </c>
@@ -4905,7 +4908,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>42</v>
       </c>
@@ -4928,7 +4931,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>42</v>
       </c>
@@ -4951,7 +4954,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>42</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
         <v>42</v>
       </c>
@@ -4997,7 +5000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>42</v>
       </c>
@@ -5020,7 +5023,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>42</v>
       </c>
@@ -5043,7 +5046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>42</v>
       </c>
@@ -5066,7 +5069,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>42</v>
       </c>
@@ -5089,7 +5092,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>42</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>42</v>
       </c>
@@ -5135,7 +5138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>42</v>
       </c>
@@ -5158,7 +5161,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
         <v>42</v>
       </c>
@@ -5181,7 +5184,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>42</v>
       </c>
@@ -5204,7 +5207,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
         <v>42</v>
       </c>
@@ -5227,7 +5230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>42</v>
       </c>
@@ -5250,7 +5253,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>42</v>
       </c>
@@ -5273,7 +5276,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
         <v>42</v>
       </c>
@@ -5296,7 +5299,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>42</v>
       </c>
@@ -5319,7 +5322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="7" t="s">
         <v>42</v>
       </c>
@@ -5342,7 +5345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>42</v>
       </c>
@@ -5365,7 +5368,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
         <v>42</v>
       </c>
@@ -5388,7 +5391,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>42</v>
       </c>
@@ -5411,7 +5414,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
         <v>42</v>
       </c>
@@ -5434,7 +5437,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>42</v>
       </c>
@@ -5457,7 +5460,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
         <v>42</v>
       </c>
@@ -5480,7 +5483,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>42</v>
       </c>
@@ -5503,7 +5506,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>42</v>
       </c>
@@ -5526,7 +5529,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>42</v>
       </c>
@@ -5549,7 +5552,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
         <v>42</v>
       </c>
@@ -5572,7 +5575,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>42</v>
       </c>
@@ -5595,7 +5598,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="7" t="s">
         <v>42</v>
       </c>
@@ -5618,7 +5621,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>42</v>
       </c>
@@ -5641,7 +5644,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
         <v>42</v>
       </c>
@@ -5664,7 +5667,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>42</v>
       </c>
@@ -5687,7 +5690,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="7" t="s">
         <v>42</v>
       </c>
@@ -5710,7 +5713,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
         <v>42</v>
       </c>
@@ -5733,7 +5736,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
         <v>42</v>
       </c>
@@ -5756,7 +5759,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>42</v>
       </c>
@@ -5779,7 +5782,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="7" t="s">
         <v>42</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="7" t="s">
         <v>42</v>
       </c>
@@ -5825,7 +5828,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="7" t="s">
         <v>42</v>
       </c>
@@ -5848,7 +5851,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="7" t="s">
         <v>42</v>
       </c>
@@ -5871,7 +5874,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="7" t="s">
         <v>42</v>
       </c>
@@ -5894,7 +5897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
         <v>42</v>
       </c>
@@ -5917,7 +5920,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="7" t="s">
         <v>42</v>
       </c>
@@ -5940,7 +5943,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>42</v>
       </c>
@@ -5963,7 +5966,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="7" t="s">
         <v>42</v>
       </c>
@@ -5986,7 +5989,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
         <v>42</v>
       </c>
@@ -6009,7 +6012,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="7" t="s">
         <v>42</v>
       </c>
@@ -6032,7 +6035,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="7" t="s">
         <v>42</v>
       </c>
@@ -6055,7 +6058,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="7" t="s">
         <v>42</v>
       </c>
@@ -6078,7 +6081,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>42</v>
       </c>
@@ -6101,7 +6104,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="7" t="s">
         <v>42</v>
       </c>
@@ -6124,7 +6127,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="7" t="s">
         <v>42</v>
       </c>
@@ -6147,7 +6150,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="7" t="s">
         <v>42</v>
       </c>
@@ -6170,7 +6173,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
         <v>42</v>
       </c>
@@ -6193,7 +6196,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
         <v>42</v>
       </c>
@@ -6216,7 +6219,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
         <v>42</v>
       </c>
@@ -6239,7 +6242,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="7" t="s">
         <v>42</v>
       </c>
@@ -6262,7 +6265,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>42</v>
       </c>
@@ -6285,7 +6288,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="7" t="s">
         <v>42</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
         <v>42</v>
       </c>
@@ -6331,7 +6334,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
         <v>42</v>
       </c>
@@ -6354,7 +6357,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="7" t="s">
         <v>42</v>
       </c>
@@ -6377,7 +6380,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="7" t="s">
         <v>42</v>
       </c>
@@ -6400,7 +6403,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="7" t="s">
         <v>42</v>
       </c>
@@ -6423,7 +6426,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="7" t="s">
         <v>42</v>
       </c>
@@ -6446,7 +6449,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="7" t="s">
         <v>42</v>
       </c>
@@ -6469,7 +6472,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="7" t="s">
         <v>42</v>
       </c>
@@ -6492,7 +6495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>42</v>
       </c>
@@ -6515,7 +6518,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="7" t="s">
         <v>42</v>
       </c>
@@ -6538,7 +6541,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="7" t="s">
         <v>42</v>
       </c>
@@ -6561,7 +6564,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="7" t="s">
         <v>42</v>
       </c>
@@ -6584,7 +6587,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="7" t="s">
         <v>42</v>
       </c>
@@ -6607,7 +6610,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="7" t="s">
         <v>42</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="7" t="s">
         <v>42</v>
       </c>
@@ -6653,7 +6656,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="7" t="s">
         <v>42</v>
       </c>
@@ -6676,7 +6679,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>42</v>
       </c>
@@ -6699,7 +6702,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="7" t="s">
         <v>42</v>
       </c>
@@ -6722,7 +6725,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="7" t="s">
         <v>42</v>
       </c>
@@ -6745,7 +6748,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="7" t="s">
         <v>42</v>
       </c>
@@ -6768,7 +6771,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
         <v>42</v>
       </c>
@@ -6791,7 +6794,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="7" t="s">
         <v>42</v>
       </c>
@@ -6814,7 +6817,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="7" t="s">
         <v>42</v>
       </c>
@@ -6837,7 +6840,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="7" t="s">
         <v>42</v>
       </c>
@@ -6860,7 +6863,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="7" t="s">
         <v>42</v>
       </c>
@@ -6883,7 +6886,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
         <v>42</v>
       </c>
@@ -6906,7 +6909,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="7" t="s">
         <v>42</v>
       </c>
@@ -6929,7 +6932,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
         <v>42</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="7" t="s">
         <v>42</v>
       </c>
@@ -6975,7 +6978,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="7" t="s">
         <v>42</v>
       </c>
@@ -6998,7 +7001,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="7" t="s">
         <v>42</v>
       </c>
@@ -7021,7 +7024,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="7" t="s">
         <v>42</v>
       </c>
@@ -7044,7 +7047,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="7" t="s">
         <v>42</v>
       </c>
@@ -7067,7 +7070,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="7" t="s">
         <v>42</v>
       </c>
@@ -7090,7 +7093,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="7" t="s">
         <v>42</v>
       </c>
@@ -7113,7 +7116,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="7" t="s">
         <v>42</v>
       </c>
@@ -7136,7 +7139,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="7" t="s">
         <v>42</v>
       </c>
@@ -7159,7 +7162,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="7" t="s">
         <v>42</v>
       </c>
@@ -7182,7 +7185,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
         <v>42</v>
       </c>
@@ -7205,7 +7208,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="9" t="s">
         <v>42</v>
       </c>
@@ -7229,21 +7232,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G250" xr:uid="{156349CF-6280-4CD0-803A-013CF8C0A2F2}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -7478,6 +7473,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7490,14 +7494,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39FDDE8C-0A1E-4704-A23F-A36DCD77389B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A89C6CB-9C03-4AE9-BB36-D0188DD65F32}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7516,6 +7512,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39FDDE8C-0A1E-4704-A23F-A36DCD77389B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C58ACE5-5395-40A6-B201-757ED1E50D7A}">
   <ds:schemaRefs>

--- a/Lista_Nacala_Porto_Turmas.xlsx
+++ b/Lista_Nacala_Porto_Turmas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{F0ECD2CA-1AFC-4D72-92BC-085899DFC072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72CCFE79-889A-4ACC-8210-E6E1F573723B}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{F0ECD2CA-1AFC-4D72-92BC-085899DFC072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F7AA41E-0463-4B67-974D-A50F65EF7072}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{619861BA-25F5-43D2-A075-305249973C9B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$251</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="285">
   <si>
     <t>Distrito</t>
   </si>
@@ -891,6 +891,9 @@
   </si>
   <si>
     <t>RAMUGI MARTINHO COVAHA</t>
+  </si>
+  <si>
+    <t>MAIASSA NAHOTO</t>
   </si>
 </sst>
 </file>
@@ -1152,6 +1155,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1471,17 +1478,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156349CF-6280-4CD0-803A-013CF8C0A2F2}">
-  <dimension ref="A1:G250"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G251"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1511,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>42</v>
       </c>
@@ -1527,7 +1534,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>42</v>
       </c>
@@ -1550,7 +1557,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>42</v>
       </c>
@@ -1573,7 +1580,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>42</v>
       </c>
@@ -1596,7 +1603,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>42</v>
       </c>
@@ -1619,7 +1626,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>42</v>
       </c>
@@ -1642,7 +1649,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>42</v>
       </c>
@@ -1665,7 +1672,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>42</v>
       </c>
@@ -1688,7 +1695,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>42</v>
       </c>
@@ -1711,7 +1718,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>42</v>
       </c>
@@ -1734,7 +1741,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1757,7 +1764,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>42</v>
       </c>
@@ -1780,7 +1787,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>42</v>
       </c>
@@ -1803,7 +1810,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
@@ -1826,7 +1833,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
@@ -1849,7 +1856,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>42</v>
       </c>
@@ -1872,7 +1879,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
@@ -1895,7 +1902,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>42</v>
       </c>
@@ -1918,7 +1925,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
@@ -1941,7 +1948,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
@@ -1964,7 +1971,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>42</v>
       </c>
@@ -1987,7 +1994,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>42</v>
       </c>
@@ -2010,7 +2017,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>42</v>
       </c>
@@ -2033,7 +2040,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -2056,7 +2063,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>42</v>
       </c>
@@ -2079,7 +2086,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>42</v>
       </c>
@@ -2102,7 +2109,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>42</v>
       </c>
@@ -2125,7 +2132,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>42</v>
       </c>
@@ -2148,7 +2155,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
@@ -2171,7 +2178,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>42</v>
       </c>
@@ -2194,7 +2201,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>42</v>
       </c>
@@ -2217,7 +2224,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>42</v>
       </c>
@@ -2240,7 +2247,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>42</v>
       </c>
@@ -2263,7 +2270,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>42</v>
       </c>
@@ -2286,7 +2293,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>42</v>
       </c>
@@ -2309,7 +2316,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>42</v>
       </c>
@@ -2332,7 +2339,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>42</v>
       </c>
@@ -2355,7 +2362,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>42</v>
       </c>
@@ -2378,7 +2385,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>42</v>
       </c>
@@ -2401,7 +2408,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>42</v>
       </c>
@@ -2424,7 +2431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -2447,7 +2454,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>42</v>
       </c>
@@ -2470,7 +2477,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>42</v>
       </c>
@@ -2493,7 +2500,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>42</v>
       </c>
@@ -2516,7 +2523,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>42</v>
       </c>
@@ -2539,7 +2546,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>42</v>
       </c>
@@ -2562,7 +2569,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>42</v>
       </c>
@@ -2585,7 +2592,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>42</v>
       </c>
@@ -2608,7 +2615,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>42</v>
       </c>
@@ -2631,7 +2638,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>42</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>42</v>
       </c>
@@ -2677,7 +2684,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>42</v>
       </c>
@@ -2700,7 +2707,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>42</v>
       </c>
@@ -2723,7 +2730,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>42</v>
       </c>
@@ -2746,7 +2753,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>42</v>
       </c>
@@ -2769,7 +2776,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>42</v>
       </c>
@@ -2792,7 +2799,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>42</v>
       </c>
@@ -2815,7 +2822,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>42</v>
       </c>
@@ -2838,7 +2845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>42</v>
       </c>
@@ -2861,7 +2868,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>42</v>
       </c>
@@ -2884,7 +2891,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>42</v>
       </c>
@@ -2907,7 +2914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>42</v>
       </c>
@@ -2930,7 +2937,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>42</v>
       </c>
@@ -2953,7 +2960,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>42</v>
       </c>
@@ -2976,7 +2983,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>42</v>
       </c>
@@ -2999,7 +3006,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>42</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>42</v>
       </c>
@@ -3045,12 +3052,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>55</v>
@@ -3068,35 +3075,35 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>84</v>
@@ -3114,12 +3121,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>84</v>
@@ -3137,12 +3144,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>84</v>
@@ -3160,12 +3167,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>84</v>
@@ -3183,18 +3190,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>43</v>
@@ -3206,12 +3213,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>84</v>
@@ -3229,12 +3236,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>84</v>
@@ -3252,12 +3259,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>84</v>
@@ -3275,12 +3282,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>84</v>
@@ -3298,12 +3305,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>84</v>
@@ -3321,12 +3328,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>84</v>
@@ -3344,12 +3351,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>84</v>
@@ -3367,12 +3374,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>84</v>
@@ -3390,18 +3397,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>43</v>
@@ -3413,12 +3420,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>84</v>
@@ -3436,12 +3443,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>84</v>
@@ -3459,12 +3466,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>84</v>
@@ -3482,18 +3489,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>43</v>
@@ -3505,12 +3512,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>84</v>
@@ -3528,12 +3535,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>84</v>
@@ -3551,18 +3558,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>43</v>
@@ -3574,12 +3581,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>84</v>
@@ -3597,12 +3604,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>84</v>
@@ -3620,12 +3627,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>84</v>
@@ -3643,12 +3650,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>84</v>
@@ -3666,12 +3673,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>84</v>
@@ -3689,12 +3696,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>84</v>
@@ -3712,12 +3719,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>84</v>
@@ -3735,12 +3742,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>84</v>
@@ -3758,12 +3765,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>84</v>
@@ -3781,12 +3788,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>84</v>
@@ -3804,12 +3811,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>84</v>
@@ -3827,15 +3834,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>5</v>
@@ -3847,15 +3854,15 @@
         <v>117</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>120</v>
@@ -3873,12 +3880,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>120</v>
@@ -3896,12 +3903,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>120</v>
@@ -3919,12 +3926,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>120</v>
@@ -3942,12 +3949,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>120</v>
@@ -3965,12 +3972,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>120</v>
@@ -3988,12 +3995,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>120</v>
@@ -4011,12 +4018,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>120</v>
@@ -4034,12 +4041,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>120</v>
@@ -4057,12 +4064,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>120</v>
@@ -4080,18 +4087,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>43</v>
@@ -4103,12 +4110,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>120</v>
@@ -4126,12 +4133,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>120</v>
@@ -4149,12 +4156,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>120</v>
@@ -4172,12 +4179,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>120</v>
@@ -4195,12 +4202,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>120</v>
@@ -4218,12 +4225,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>120</v>
@@ -4241,12 +4248,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>120</v>
@@ -4264,12 +4271,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>120</v>
@@ -4287,12 +4294,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>120</v>
@@ -4310,18 +4317,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>43</v>
@@ -4333,12 +4340,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>120</v>
@@ -4356,12 +4363,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>120</v>
@@ -4379,18 +4386,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>43</v>
@@ -4402,12 +4409,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>120</v>
@@ -4425,12 +4432,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>120</v>
@@ -4448,12 +4455,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>120</v>
@@ -4471,12 +4478,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>120</v>
@@ -4494,12 +4501,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>120</v>
@@ -4517,12 +4524,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>120</v>
@@ -4540,12 +4547,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>120</v>
@@ -4563,17 +4570,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C135" s="2" t="s">
+      <c r="B135" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E135" s="1" t="s">
@@ -4586,17 +4593,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C136" s="1" t="s">
+      <c r="B136" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E136" s="1" t="s">
@@ -4609,12 +4616,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>120</v>
@@ -4632,12 +4639,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>120</v>
@@ -4655,12 +4662,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>120</v>
@@ -4678,12 +4685,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>120</v>
@@ -4701,12 +4708,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>120</v>
@@ -4724,38 +4731,38 @@
         <v>49</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C143" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>5</v>
@@ -4770,12 +4777,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>188</v>
@@ -4793,12 +4800,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>188</v>
@@ -4816,17 +4823,17 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D146" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E146" s="1" t="s">
@@ -4839,17 +4846,17 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D147" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E147" s="1" t="s">
@@ -4862,15 +4869,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>5</v>
@@ -4885,15 +4892,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>5</v>
@@ -4908,12 +4915,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>188</v>
@@ -4931,15 +4938,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>5</v>
@@ -4954,15 +4961,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>5</v>
@@ -4977,15 +4984,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>5</v>
@@ -5000,18 +5007,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>43</v>
@@ -5023,12 +5030,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>188</v>
@@ -5046,12 +5053,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>188</v>
@@ -5069,12 +5076,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>188</v>
@@ -5092,12 +5099,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>188</v>
@@ -5115,12 +5122,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>188</v>
@@ -5138,12 +5145,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>188</v>
@@ -5161,12 +5168,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>188</v>
@@ -5184,12 +5191,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>188</v>
@@ -5207,12 +5214,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>188</v>
@@ -5230,12 +5237,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>188</v>
@@ -5253,12 +5260,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>188</v>
@@ -5276,12 +5283,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>188</v>
@@ -5299,18 +5306,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>43</v>
@@ -5322,12 +5329,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>188</v>
@@ -5345,12 +5352,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>188</v>
@@ -5368,12 +5375,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>188</v>
@@ -5391,12 +5398,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>188</v>
@@ -5411,15 +5418,15 @@
         <v>190</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>188</v>
@@ -5437,12 +5444,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>188</v>
@@ -5460,12 +5467,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>188</v>
@@ -5483,12 +5490,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>188</v>
@@ -5506,12 +5513,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>188</v>
@@ -5529,12 +5536,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>188</v>
@@ -5552,12 +5559,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>188</v>
@@ -5575,12 +5582,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>188</v>
@@ -5598,12 +5605,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>188</v>
@@ -5621,12 +5628,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>188</v>
@@ -5644,12 +5651,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>188</v>
@@ -5667,12 +5674,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>188</v>
@@ -5690,12 +5697,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>188</v>
@@ -5713,12 +5720,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>188</v>
@@ -5736,12 +5743,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>188</v>
@@ -5759,12 +5766,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>188</v>
@@ -5782,12 +5789,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>188</v>
@@ -5805,12 +5812,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>188</v>
@@ -5828,12 +5835,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>188</v>
@@ -5851,18 +5858,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>43</v>
@@ -5874,12 +5881,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>188</v>
@@ -5897,18 +5904,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>43</v>
@@ -5920,12 +5927,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>188</v>
@@ -5943,12 +5950,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>188</v>
@@ -5966,12 +5973,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>188</v>
@@ -5989,18 +5996,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>43</v>
@@ -6012,12 +6019,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>188</v>
@@ -6035,12 +6042,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>188</v>
@@ -6058,35 +6065,35 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>220</v>
@@ -6104,12 +6111,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>220</v>
@@ -6127,12 +6134,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>220</v>
@@ -6150,12 +6157,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>220</v>
@@ -6173,12 +6180,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>220</v>
@@ -6196,12 +6203,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>220</v>
@@ -6219,12 +6226,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>220</v>
@@ -6242,12 +6249,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>220</v>
@@ -6265,12 +6272,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>220</v>
@@ -6288,12 +6295,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>220</v>
@@ -6311,18 +6318,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>43</v>
@@ -6334,12 +6341,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>220</v>
@@ -6357,12 +6364,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>220</v>
@@ -6380,12 +6387,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>220</v>
@@ -6403,12 +6410,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>220</v>
@@ -6426,18 +6433,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>43</v>
@@ -6449,18 +6456,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>43</v>
@@ -6472,12 +6479,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>220</v>
@@ -6495,18 +6502,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>43</v>
@@ -6518,12 +6525,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>220</v>
@@ -6541,12 +6548,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>220</v>
@@ -6564,12 +6571,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>220</v>
@@ -6587,12 +6594,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>220</v>
@@ -6610,18 +6617,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>43</v>
@@ -6633,18 +6640,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>43</v>
@@ -6656,12 +6663,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>220</v>
@@ -6679,12 +6686,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>220</v>
@@ -6702,15 +6709,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>5</v>
@@ -6722,15 +6729,15 @@
         <v>244</v>
       </c>
       <c r="G228" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>246</v>
@@ -6748,12 +6755,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>246</v>
@@ -6771,12 +6778,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>246</v>
@@ -6794,12 +6801,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>246</v>
@@ -6817,12 +6824,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>246</v>
@@ -6840,12 +6847,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>246</v>
@@ -6863,12 +6870,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>246</v>
@@ -6886,12 +6893,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>246</v>
@@ -6909,12 +6916,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>246</v>
@@ -6932,18 +6939,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>43</v>
@@ -6955,15 +6962,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>21</v>
@@ -6978,12 +6985,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>246</v>
@@ -7001,12 +7008,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>246</v>
@@ -7024,12 +7031,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>246</v>
@@ -7047,12 +7054,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>246</v>
@@ -7070,18 +7077,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>43</v>
@@ -7093,18 +7100,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>43</v>
@@ -7116,12 +7123,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>246</v>
@@ -7139,12 +7146,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>246</v>
@@ -7162,12 +7169,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>246</v>
@@ -7185,12 +7192,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>246</v>
@@ -7208,37 +7215,69 @@
         <v>53</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A250" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B250" s="10" t="s">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A250" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B251" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="C250" s="10" t="s">
+      <c r="C251" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D250" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E250" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F250" s="10" t="s">
+      <c r="D251" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F251" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="G250" s="11" t="s">
+      <c r="G251" s="11" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G250" xr:uid="{156349CF-6280-4CD0-803A-013CF8C0A2F2}"/>
+  <autoFilter ref="A1:G251" xr:uid="{156349CF-6280-4CD0-803A-013CF8C0A2F2}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -7473,15 +7512,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7494,6 +7524,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39FDDE8C-0A1E-4704-A23F-A36DCD77389B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A89C6CB-9C03-4AE9-BB36-D0188DD65F32}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7512,14 +7550,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39FDDE8C-0A1E-4704-A23F-A36DCD77389B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C58ACE5-5395-40A6-B201-757ED1E50D7A}">
   <ds:schemaRefs>
